--- a/public/templates/template_status_change.xlsx
+++ b/public/templates/template_status_change.xlsx
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>hemicode</v>
+        <v>cn_code</v>
       </c>
     </row>
     <row r="2">
